--- a/templates/RoadCoda-template-Drivers.xlsx
+++ b/templates/RoadCoda-template-Drivers.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,6 +59,12 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
@@ -78,7 +84,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -98,6 +104,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF1B8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C00000"/>
       </patternFill>
     </fill>
     <fill>
@@ -132,7 +143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -149,35 +160,38 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -265,7 +279,8 @@
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
         <t>REQUIRED. First and last name, as on the CDL.
-Example: Carlos Martinez</t>
+Example: Carlos Martinez
+NEVER include Social Security numbers or bank details. RoadCoda does not store them.</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
@@ -17771,7 +17786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -17830,369 +17845,377 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+    <row r="9" ht="48" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>NEVER put Social Security numbers, bank account or routing numbers in this file. RoadCoda has no place for them and does not store them: the upload ignores them, and any file sent to RoadCoda that contains them is deleted. If you include them anyway, you do so at your own risk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>Required?</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>What to enter</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>Example</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Allowed values</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>Full Name</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t>First and last name, as on the CDL.</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>Carlos Martinez</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>Mobile number. Used to sign the driver into the app.</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t>(860) 555-0123</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr"/>
-      <c r="C13" s="14" t="inlineStr"/>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr"/>
+      <c r="C15" s="15" t="inlineStr"/>
+      <c r="D15" s="16" t="inlineStr">
         <is>
           <t>cmartinez@example.com</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="16" t="inlineStr">
+      <c r="E15" s="15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>Employee #</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>Recommended — Payroll company files (ADP, Paychex, Gusto…) match drivers by it.</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C16" s="18" t="inlineStr">
         <is>
           <t>Your payroll number. Kept as text.</t>
         </is>
       </c>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="D16" s="19" t="inlineStr">
         <is>
           <t>00412</t>
         </is>
       </c>
-      <c r="E14" s="17" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="E16" s="18" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>Driver Type</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr"/>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr"/>
+      <c r="C17" s="15" t="inlineStr">
         <is>
           <t>Road (default), Team or Yard.</t>
         </is>
       </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="D17" s="16" t="inlineStr">
         <is>
           <t>Road</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E17" s="15" t="inlineStr">
         <is>
           <t>Road, Team, Yard</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>Hire Date</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>MM/DD/YYYY.</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>05/12/2021</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="16" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>CDL Number</t>
         </is>
       </c>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B19" s="18" t="inlineStr">
         <is>
           <t>Recommended — Driver file and compliance.</t>
         </is>
       </c>
-      <c r="C17" s="17" t="inlineStr">
+      <c r="C19" s="18" t="inlineStr">
         <is>
           <t>Kept as text.</t>
         </is>
       </c>
-      <c r="D17" s="18" t="inlineStr">
+      <c r="D19" s="19" t="inlineStr">
         <is>
           <t>123456789</t>
         </is>
       </c>
-      <c r="E17" s="17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="E19" s="18" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>CDL State</t>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B20" s="18" t="inlineStr">
         <is>
           <t>Recommended — Driver file and compliance.</t>
         </is>
       </c>
-      <c r="C18" s="17" t="inlineStr">
+      <c r="C20" s="18" t="inlineStr">
         <is>
           <t>Two letters.</t>
         </is>
       </c>
-      <c r="D18" s="18" t="inlineStr">
+      <c r="D20" s="19" t="inlineStr">
         <is>
           <t>CT</t>
         </is>
       </c>
-      <c r="E18" s="17" t="inlineStr">
+      <c r="E20" s="18" t="inlineStr">
         <is>
           <t>2-letter state</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="16" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>CDL Class</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B21" s="18" t="inlineStr">
         <is>
           <t>Recommended — Driver file and compliance.</t>
         </is>
       </c>
-      <c r="C19" s="17" t="inlineStr">
+      <c r="C21" s="18" t="inlineStr">
         <is>
           <t>A, B, C, or none.</t>
         </is>
       </c>
-      <c r="D19" s="18" t="inlineStr">
+      <c r="D21" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="E19" s="17" t="inlineStr">
+      <c r="E21" s="18" t="inlineStr">
         <is>
           <t>A, B, C, none</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="16" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>CDL Expires</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B22" s="18" t="inlineStr">
         <is>
           <t>Recommended — CDL expiry alert — a safety and legal requirement.</t>
         </is>
       </c>
-      <c r="C20" s="17" t="inlineStr">
+      <c r="C22" s="18" t="inlineStr">
         <is>
           <t>MM/DD/YYYY.</t>
         </is>
       </c>
-      <c r="D20" s="18" t="inlineStr">
+      <c r="D22" s="19" t="inlineStr">
         <is>
           <t>08/31/2028</t>
         </is>
       </c>
-      <c r="E20" s="17" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="E22" s="18" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>Medical Card Expires</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B23" s="18" t="inlineStr">
         <is>
           <t>Recommended — Medical card expiry alert — a safety and legal requirement.</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="C23" s="18" t="inlineStr">
         <is>
           <t>MM/DD/YYYY.</t>
         </is>
       </c>
-      <c r="D21" s="18" t="inlineStr">
+      <c r="D23" s="19" t="inlineStr">
         <is>
           <t>02/28/2027</t>
         </is>
       </c>
-      <c r="E21" s="17" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="E23" s="18" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>Home Terminal</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr"/>
-      <c r="C22" s="14" t="inlineStr">
+      <c r="B24" s="15" t="inlineStr"/>
+      <c r="C24" s="15" t="inlineStr">
         <is>
           <t>The terminal name, if you have more than one.</t>
         </is>
       </c>
-      <c r="D22" s="15" t="inlineStr">
+      <c r="D24" s="16" t="inlineStr">
         <is>
           <t>Hartford</t>
         </is>
       </c>
-      <c r="E22" s="14" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="E24" s="15" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="inlineStr">
         <is>
           <t>Emergency Contact</t>
         </is>
       </c>
-      <c r="B23" s="17" t="inlineStr">
+      <c r="B25" s="18" t="inlineStr">
         <is>
           <t>Recommended — Who to call if something happens on the road.</t>
         </is>
       </c>
-      <c r="C23" s="17" t="inlineStr"/>
-      <c r="D23" s="18" t="inlineStr">
+      <c r="C25" s="18" t="inlineStr"/>
+      <c r="D25" s="19" t="inlineStr">
         <is>
           <t>Maria Martinez</t>
         </is>
       </c>
-      <c r="E23" s="17" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="16" t="inlineStr">
+      <c r="E25" s="18" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="inlineStr">
         <is>
           <t>Emergency Phone</t>
         </is>
       </c>
-      <c r="B24" s="17" t="inlineStr">
+      <c r="B26" s="18" t="inlineStr">
         <is>
           <t>Recommended — Who to call if something happens on the road.</t>
         </is>
       </c>
-      <c r="C24" s="17" t="inlineStr"/>
-      <c r="D24" s="18" t="inlineStr">
+      <c r="C26" s="18" t="inlineStr"/>
+      <c r="D26" s="19" t="inlineStr">
         <is>
           <t>(860) 555-0199</t>
         </is>
       </c>
-      <c r="E24" s="17" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="E26" s="18" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="B25" s="14" t="inlineStr"/>
-      <c r="C25" s="14" t="inlineStr">
+      <c r="B27" s="15" t="inlineStr"/>
+      <c r="C27" s="15" t="inlineStr">
         <is>
           <t>Office only.</t>
         </is>
       </c>
-      <c r="D25" s="15" t="inlineStr">
+      <c r="D27" s="16" t="inlineStr">
         <is>
           <t>Prefers early starts</t>
         </is>
       </c>
-      <c r="E25" s="14" t="inlineStr"/>
+      <c r="E27" s="15" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A7:E7"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A8:E8"/>
     <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A9:E9"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
